--- a/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,7 +513,7 @@
     <t>The overall type of event, intended for search and filtering purposes.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260916095453</t>
   </si>
   <si>
     <t>AdverseEvent.event</t>
@@ -672,7 +672,7 @@
     <t>Describes the severity of the adverse event, in relation to the subject. Contrast to AdverseEvent.seriousness - a severe rash might not be serious, but a mild heart problem is.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260916095454</t>
   </si>
   <si>
     <t>AdverseEvent.outcome</t>
@@ -684,7 +684,7 @@
     <t>Describes the type of outcome from the adverse event.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260916095454</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>

--- a/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
